--- a/School_Data.xlsx
+++ b/School_Data.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1939,20 +1939,16 @@
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1679428506</t>
-        </is>
+      <c r="B39" t="n">
+        <v>1679428506</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>القسمة-التقسيم المتساوي</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D39" t="n">
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>3</v>
@@ -2011,6 +2007,467 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1679428506</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>الكسورأجزاء من الكل</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>### خطة درس أولية: الكسور أجزاء من الكل
+**الموضوع:** الكسور: أنصاف، أثلاث، أرباع وحتى جزء من 12  
+**المدة:** 40 دقيقة  
+**الفئة العمرية:** الصف الثالث/الرابع  
+**فجوة التعلم:** 25.0%  
+**اتجاه الأداء:** مستقر (بداية)  
+**مستوى الدقة الحالية:** 0.75  
+**الاستراتيجية:** التعلم النشط (التعلم المتمركز حول الطالب)  
+#### الأهداف:
+1. تعريف الطلاب بمفهوم الكسور (أنصاف، أثلاث، أرباع، أجزاء من 12).
+2. تمكين الطلاب من تحديد الكسور المختلفة وتمثيلها بصريًا.
+3. تعزيز مهارات التعاون والعمل الجماعي بين الطلاب.
+#### 🎮 **النشاط التفاعلي المقترح:** لعبة "محطات الكسور"
+**المعدات المطلوبة:**
+- بطاقات تحتوي على صور تمثل الكسور (مثل نصف، ثلث، ربع).
+- أدوات قياس (مثل مساطر، كرات، قطع من الورق).
+- ورق عمل لمتابعة الأداء.
+- أدوات فنية (أقلام، ألوان).
+---
+### خطوات 🎮 **النشاط التفاعلي المقترح:**
+#### المحطة 1: تعريف الكسور (5 دقائق)
+- **وصف المحطة:** يشرح المعلم مفهوم الكسور للطلاب باستخدام أدوات بصرية.
+- **🎮 **النشاط التفاعلي المقترح:**** الطلاب يشاركون في نقاش حول الكسور، ويقومون برسم الكسور التي تم شرحها.
+#### المحطة 2: محطة القياس (10 دقائق)
+- **وصف المحطة:** استخدام أدوات قياس لتجسيد الكسور.
+- **🎮 **النشاط التفاعلي المقترح:**** يقوم الطلاب بقياس أشياء في الفصل وكتابة الكسر المناسب. مثال: قياس طول كتاب باستخدام المسطرة وتحديد الكسر المناسب للقياس.
+#### المحطة 3: محطة التمثيل البصري (10 دقائق)
+- **وصف المحطة:** تمثيل الكسور باستخدام الألوان.
+- **🎮 **النشاط التفاعلي المقترح:**** الطلاب يملأون ورقة عمل تحتوي على أشكال تتطلب منهم تلوين أجزاء من الشكل لتظهر الكسور (مثل نصف دائرة، ثلث مربع).
+#### المحطة 4: لعبة الأدوار (10 دقائق)
+- **وصف المحطة:** الطلاب يتوزعون في مجموعات صغيرة لأداء أدوار مختلفة (مثل تاجر وعميل).
+- **🎮 **النشاط التفاعلي المقترح:**** يقوم الطلاب بتمثيل عملية شراء باستخدام الكسور (مثل "أريد ربع كيلو من التفاح"). يجب على كل مجموعة تقديم تقرير عن الأدوار التي قاموا بها.
+#### المحطة 5: مراجعة وتقييم (5 دقائق)
+- **وصف المحطة:** مراجعة ما تم تعلمه.
+- **🎮 **النشاط التفاعلي المقترح:**** يقوم المعلم بطرح أسئلة على الطلاب حول ما تعلموه، ويعطيهم فرص لتطبيق المعرفة من خلال حل مشكلات بسيطة.
+---
+### 📝 **أداة قياس الأثر:**
+- سيتم تقييم الطلاب بناءً على مشاركتهم في الأنشطة والتفاعل في النقاشات.
+- سيقوم المعلم بتوزيع ورقة عمل تحتوي على أسئلة حول الكسور في نهاية النشاط، لتقييم مدى فهم الطلاب.
+### ملاحظات:
+- التأكد من توفير بيئة تعليمية مشجعة.
+- توفير الدعم الإضافي للطلاب الذين يحتاجون إلى مساعدة إضافية.
+- التجهيز المسبق للمواد اللازمة لكل محطة لضمان سلاسة الدرس.
+### الخاتمة:
+بعد هذا النشاط، سيكون الطلاب قد اكتسبوا فهمًا أفضل لمفهوم الكسور، مما يساعد في تقليل فجوة التعلم وتحسين اتجاه الأداء.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1679428506</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>الطرح البسيط</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>**خطة درس أولية: الطرح البسيط**
+**الموضوع:** الطرح البسيط  
+**🎯 **الهدف التربوي:**** فهم مفهوم الطرح كأخذ جزء من الكل  
+**الفئة المستهدفة:** طلاب الصف الأول الابتدائي  
+**المدة:** 40 دقيقة  
+**استراتيجية التعلم:** التعلم المتمركز حول الطالب (Student-Centered)  
+**فجوة التعلم:** 25.0%  
+**اتجاه الأداء:** مستقر (بداية)  
+### **أهداف الدرس:**
+1. تعريف الطلاب بمفهوم الطرح كعملية أخذ جزء من الكل.
+2. تمكين الطلاب من إجراء عمليات الطرح البسيطة باستخدام الأعداد من 1 إلى 10.
+3. تعزيز الفهم من خلال التجربة العملية واللعب.
+### **المواد المطلوبة:**
+- كرات ملونة (عدد 20 كرة)
+- بطاقات أرقام (من 1 إلى 10)
+- أوراق عمل (تحتوي على مسائل طرح بسيطة)
+- أدوات فنية (أقلام، ورق، إلخ)
+### **محطات النشاط التعليمية:**
+1. **محطة التعريف (10 دقائق):**
+   - **🎮 **النشاط التفاعلي المقترح:**** يبدأ المعلم بشرح مفهوم الطرح باستخدام الكرات الملونة. يعرض 10 كرات ويُظهر كيف يمكن أخذ 3 منها، ويطرح سؤال: "كم كرة تبقى؟".
+   - **التفاعل:** يُشرك الطلاب في تحديد عدد الكرات المتبقية، ويشجعهم على استخدام أيديهم لتمثيل العملية.
+2. **محطة اللعب التمثيلي (15 دقيقة):**
+   - **🎮 **النشاط التفاعلي المقترح:**** تقسيم الطلاب إلى مجموعتين. تستخدم كل مجموعة الكرات الملونة لأداء تمثيلية قصيرة. على سبيل المثال، واحدة من المجموعات تمثل "المخزن" والأخرى تمثل "الزبائن". يمكن للزبائن أخذ كرات من المخزن.
+   - **التفاعل:** يُطلب من الطلاب حساب عدد الكرات المتبقية في المخزن بعد أن يأخذ الزبائن بعض الكرات، مما يعزز الفهم العملي لمفهوم الطرح.
+3. **محطة الأنشطة الكتابية (10 دقائق):**
+   - **🎮 **النشاط التفاعلي المقترح:**** توزيع أوراق العمل على الطلاب، تحتوي على مسائل طرح بسيطة. يجب عليهم حل هذه المسائل بشكل فردي.
+   - **التفاعل:** يقوم المعلم بجولة لمساعدة الطلاب الذين يحتاجون إلى دعم إضافي، مع التركيز على طلاب الفجوة التعليمية العالية.
+4. **محطة المراجعة الجماعية (5 دقائق):**
+   - **🎮 **النشاط التفاعلي المقترح:**** يجتمع الطلاب في دائرة ويتبادلون الحديث حول ما تعلموه. يمكن للمعلم أن يطرح أسئلة مفتوحة مثل "ما هو الطرح؟" و"كيف يمكننا استخدامه في الحياة اليومية؟".
+   - **التفاعل:** يشجع المعلم على مشاركة الأفكار والنتائج التي توصل إليها الطلاب، مما يعزز التعلم الجماعي.
+### **📝 **أداة قياس الأثر:****
+- مراقبة تفاعل الطلاب في المحطات المختلفة.
+- تقييم أوراق العمل الخاصة بالطلاب.
+- إجراء مناقشة قصيرة في النهاية لتحديد ما إذا كانت الفجوة التعليمية قد تمت معالجتها.
+### **الملاحظات:**
+- التأكد من أن جميع الطلاب يشاركون ويشعرون بالراحة أثناء النشاطات.
+- استخدام التقنيات التعليمية لتحفيز الطلاب وتحقيق نتائج أفضل في فهم الطرح. 
+بتطبيق هذه الخطة، يتوقع أن يتحسن فهم الطلاب لمفهوم الطرح كأخذ جزء من الكل، ويُعالج الفجوة التعليمية بشكل فعال.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1679428506</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>الوقت</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>### خطة درس أولية: 'الوقت' - قراءة الساعة بالتمام وبنصف ساعة
+#### 🎯 **الهدف التربوي:** 
+تمكين الطلاب من قراءة الساعة بالتمام وبنصف ساعة.
+#### الفئة المستهدفة:
+طلاب المرحلة الابتدائية (الصف الثاني أو الثالث).
+#### المدة: 
+40 دقيقة.
+#### الفجوة التعليمية:
+25.0% (تحقيق مستوى دقة 0.75).
+#### الاستراتيجية المقترحة: 
+استراتيجية التعلم النشط مع التركيز على التفاعل والمشاركة.
+### محتوى 🎮 **النشاط التفاعلي المقترح:**
+#### المحطة الأولى: التعرف على الساعة (10 دقائق)
+- **🎯 **الهدف التربوي:**** تعريف الطلاب بأجزاء الساعة (العقارب، الأرقام، الفواصل الزمنية).
+- **🎮 **النشاط التفاعلي المقترح:**** استخدام ساعة حقيقية أو نموذجية لشرح أجزاء الساعة. 
+- **التفاعل:** اطلب من الطلاب تمييز العقارب (الساعات والدقائق) والإشارة إلى الأوقات المحددة.
+#### المحطة الثانية: اللعبة التعليمية 'سوق الوقت' (15 دقيقة)
+- **🎯 **الهدف التربوي:**** ممارسة قراءة الساعة في بيئة تفاعلية.
+- **🎮 **النشاط التفاعلي المقترح:**** 
+   - إعداد محطات صغيرة تمثل 'سوق الوقت' حيث يمكن للطلاب التحرك بين المحطات.
+   - في كل محطة، سيتم عرض مجموعة من الساعات بأوقات مختلفة. 
+   - يجب على الطلاب قراءة الوقت المكتوب على الساعة، ثم تسجيله على بطاقات خاصة.
+- **التفاعل:** كل طالب يقوم بتبادل البطاقات مع زملائه في المحطة للحصول على تعليقات فورية حول إجاباتهم.
+#### المحطة الثالثة: العروض التقديمية (10 دقائق)
+- **🎯 **الهدف التربوي:**** تعزيز الفهم من خلال المشاركة الفعالة.
+- **🎮 **النشاط التفاعلي المقترح:**** 
+   - يقوم كل طالب باختيار ساعتين من بطاقاتهم وعرضها على زملائه.
+   - يجب عليهم قراءة الوقت بصوت عالٍ، وتقديم أي صعوبات واجهتهم.
+- **التفاعل:** زملاء الطلاب يقدمون الدعم والتصحيح إذا كان هناك أخطاء في القراءة.
+#### المحطة الرابعة: التقييم الذاتي (5 دقائق)
+- **🎯 **الهدف التربوي:**** تقييم مدى تقدم الطلاب في قراءة الساعة.
+- **🎮 **النشاط التفاعلي المقترح:**** 
+   - توفير ورقة عمل تحتوي على صور لساعات مختلفة (بالتوقيت الكامل ونصف الساعة).
+   - يُطلب من الطلاب قراءة الأوقات وتدوينها.
+- **التفاعل:** الطلاب يتبادلون الأوراق مع زملائهم للحصول على تقييم سريع.
+### 📝 **أداة قياس الأثر:**
+- سيتم تقييم الطلاب بناءً على دقة إجاباتهم في ورقة العمل، والمشاركة في الأنشطة، والتعاون مع زملائهم.
+### الملاحظات النهائية:
+- تأكد من توفير بيئة تعليمية مرحة ومحفزة.
+- شجع الطلاب على العمل كفريق واحد وتبادل المعرفة فيما بينهم.
+- استخدم التعزيز الإيجابي لتحفيز الطلاب على المشاركة.
+بهذه الخطة، نكون قد صممنا نشاطًا تعليميًا عميقًا يتناسب مع الفجوة التعليمية المستهدفة ويشجع على التعلم النشط والمشاركة الفعالة.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1679428506</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>الجمع مع إعادة تسمية (بمقدار 10)</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>**خطة درس أولية: الجمع مع إعادة تسمية (بمقدار 10)**
+**الهدف التعليمي:**  
+فهم تبادل 10 آحاد بعشرة واحدة.
+**المدة الزمنية:**  
+40 دقيقة
+**الفئة المستهدفة:**  
+طلاب في المرحلة الابتدائية (الصف الثالث)
+**مستوى الفجوة التعليمية:**  
+25.0%
+---
+### **المواد المطلوبة:**
+- بطاقات تعليمية تحتوي على أعداد مختلفة.
+- ألعاب لوحية صغيرة أو أوراق عمل.
+- أدوات للكتابة (أقلام، ورق).
+- ساعة توقيت.
+---
+### **الخطوات:**
+#### **1. المقدمة (5 دقائق):**
+- ابدأ بطرح سؤال بسيط: "ماذا يحدث عندما نجمع 10 آحاد؟"
+- تحدث مع الطلاب عن مفهوم إعادة التسمية وأهمية فهمه في الجمع.
+#### **2. المحطة 1: لعبة "تبادل الأعداد" (10 دقائق):**
+- قسم الطلاب إلى مجموعات صغيرة (4-5 طلاب).
+- كل مجموعة تتسلم مجموعة من البطاقات التعليمية (مثل: 8 + 5).
+- على الطلاب استخدام البطاقات لتبادل 10 آحاد بعشرة واحدة، وشرح العملية لبعضهم.
+- يتم السؤال عن النتيجة النهائية لكل مجموعة.
+#### **3. المحطة 2: ورشة "الجمع التفاعلي" (10 دقائق):**
+- وزع أوراق عمل تحتوي على مسائل جمع تتطلب إعادة تسمية (مثل: 27 + 5).
+- اطلب من الطلاب العمل بشكل فردي، ومساعدة بعضهم البعض في حل المسائل.
+- رصد المعلم لأداء الطلاب وتقديم الملاحظات.
+#### **4. المحطة 3: لعبة "منافسة الجمع" (10 دقائق):**
+- استخدم الألعاب اللوحية الصغيرة. كل طالب يلعب بمفرده.
+- عند وصول الطالب إلى نقطة معينة (مثل 10 نقاط)، يجب عليه جمع الأعداد الموجودة في نقطة البداية وتجميعها مع إعادة التسمية.
+- يتسابق الطلاب لرؤية من يستطيع الحصول على أكبر عدد من النقاط.
+#### **5. الخاتمة (5 دقائق):**
+- اجمع الطلاب واطلب منهم مشاركة ما تعلموه.
+- قدم لهم أمثلة إضافية لتدريبهم في المنزل.
+- اطرح سؤالًا: "كيف يمكن أن نستخدم إعادة التسمية في حياتنا اليومية؟".
+---
+### **📝 **أداة قياس الأثر:****
+- ملاحظة أداء الطلاب خلال الأنشطة.
+- استخدام أسئلة سريعة في النهاية لتحديد مستوى الفهم ومكان الفجوات.
+### **الملاحظات:**
+- التركيز على تعزيز العمل الجماعي والتفاعل بين الطلاب.
+- التأكد من أن كل محطة تتضمن عنصرًا من المرح لضمان التفاعل والمشاركة. 
+--- 
+بهذه الطريقة، نكون قد أعددنا نشاطًا تعليميًا يحقق الهدف التعليمي بشكل فعال ويعمل على سد الفجوة التعليمية لدى الطلاب.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1679428506</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>الجمع البسيط(بدون إعادة تسمية)</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>### خطة درس أولية: "الجمع البسيط (بدون إعادة تسمية)"
+#### الهدف التعليمي:
+جمع مجموعتين من الكميات واكتشاف النتيجة.
+#### الفئة المستهدفة:
+طلاب من الصف الثاني الابتدائي.
+#### المدة الزمنية:
+40 دقيقة.
+#### تحليل الفجوة التعليمية:
+- **فجوة التعلم**: 25.0% 
+- **اتجاه الأداء**: مستقر (بداية)
+- **مستوى الدقة الحالية**: 0.75
+#### الاستراتيجية التعليمية:
+التعلم المتمركز حول الطالب، باستخدام لعبة تعليمية عميقة (Simulation/Role Play) تتضمن محطات تعليمية متعددة.
+### خطة 🎮 **النشاط التفاعلي المقترح:**
+#### 1. المقدمة (5 دقائق):
+- ابدأ بمقدمة قصيرة عن مفهوم الجمع، واستخدم أمثلة بسيطة تتعلق بحياة الطلاب اليومية (مثل جمع الفواكه أو الألعاب).
+- اشرح أهمية الجمع في الحياة اليومية وكيف نستخدمه في مواقف مختلفة.
+#### 2. تقسيم الطلاب إلى مجموعات (5 دقائق):
+- قسم الطلاب إلى 4 مجموعات صغيرة (5 طلاب في كل مجموعة).
+- كل مجموعة ستمثل محطة تعليمية مختلفة.
+#### 3. المحطات التعليمية (25 دقيقة):
+كل محطة ستستمر لمدة 5 دقائق، وتجري كالتالي:
+- **المحطة 1: شراء الفواكه**
+  - 🎮 **النشاط التفاعلي المقترح:** كل مجموعة تمثل بائعاً ومشترياً. يطلب المشتري شراء عدد من الفواكه (مثل 3 تفاحات و2 موزات)، وعليهم جمع الكمية الكلية.
+  - الأداة: ورقة عمل لتسجيل الكميات.
+- **المحطة 2: الألعاب**
+  - 🎮 **النشاط التفاعلي المقترح:** على كل مجموعة جمع عدد معين من الألعاب (2 كرات و3 دمى) واكتشاف العدد الكلي.
+  - الأداة: مجموعة من الألعاب البلاستيكية لتوضيح النشاط.
+- **المحطة 3: الزهور**
+  - 🎮 **النشاط التفاعلي المقترح:** يتم إعطاء كل مجموعة عدد من الزهور (4 زهور حمراء و3 زهور صفراء) وعليهم جمع الكمية.
+  - الأداة: زهور ورقية.
+- **المحطة 4: النقود**
+  - 🎮 **النشاط التفاعلي المقترح:** كل مجموعة تتلقى عملات ورقية (5 عملات من فئة 1 ريال و2 عملات من فئة 5 ريالات) وعليهم جمع المبلغ الكلي.
+  - الأداة: عملات فارغة أو صور لها.
+#### 4. مناقشة ختامية (5 دقائق):
+- اجمع الطلاب في دائرة واطلب من كل مجموعة مشاركة ما تعلمته في المحطات.
+- ناقش معهم كيفية استخدام الجمع في حياتهم اليومية، وحثهم على طرح الأسئلة.
+### التقويم:
+- استخدم استبيانًا بسيطًا لتقييم مدى فهم الطلاب لمفهوم الجمع، مع أسئلة مثل: "إذا كان لديك 3 تفاحات و5 موزات، كم عدد الفواكه لديك؟".
+### الملاحظات:
+- تأكد من مراقبة تقدم الطلاب خلال النشاطات وتقديم الدعم لهم عند الحاجة.
+- استخدم أسئلة مفتوحة خلال النقاش الختامي لتعزيز التفكير النقدي لدى الطلاب.
+### الهدف النهائي:
+تحقيق الفهم العميق لمفهوم الجمع البسيط من خلال الأنشطة التفاعلية والمشاركة الفعالة للطلاب، مما يساهم في سد الفجوة التعليمية وتحسين مستوى الأداء.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1679428506</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>جمع وطرح النقود</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>### خطة درس أولية: جمع وطرح النقود
+**الموضوع**: جمع وطرح النقود  
+**المدة**: 40 دقيقة  
+**الفئة المستهدفة**: طلاب في المرحلة الابتدائية
+#### الأهداف التعليمية:
+1. فهم مفهوم جمع وطرح النقود.
+2. تطبيق مهارات جمع وطرح النقود في سياقات عملية.
+3. تعزيز التعاون والتفاعل بين الطلاب من خلال أنشطة جماعية.
+#### الفجوة التعليمية:
+**الفجوة**: 25.0%  
+**الاتجاه**: مستقر (بداية)
+#### الاستراتيجية:
+استخدام التعلم المتمركز حول الطالب من خلال لعبة تعليمية تتضمن محطات تعليمية متعددة.
+### تفاصيل 🎮 **النشاط التفاعلي المقترح:**
+#### المحطة 1: تعارف النقود (10 دقائق)
+- **المحتوى**: تعريف الطلاب بالنقود، أنواعها (عملات معدنية، ورقية) وقيمتها.
+- **النشاط**: توزيع صور لنقود مختلفة على الطلاب وطلب منهم تحديد القيمة لكل نوع.
+- **الأدوات**: صور نقود، بطاقات تتضمن القيم.
+#### المحطة 2: جمع النقود (10 دقائق)
+- **المحتوى**: كيفية جمع النقود.
+- **النشاط**: وضع مجموعة من النقود (صور أو قطع فعلية) على الطاولة، وطلب من الطلاب جمعها معًا وحساب المجموع. 
+- **الأدوات**: قطع نقدية (حقيقية أو مزيفة)، أوراق حساب.
+#### المحطة 3: طرح النقود (10 دقائق)
+- **المحتوى**: كيفية طرح النقود.
+- **النشاط**: إعطاء الطلاب سيناريوهات بسيطة (مثل: لديك 20 ريال، اشتريت شيئًا بـ 7 ريالات، كم تبقى لديك؟) وطلب منهم حساب المبلغ المتبقي.
+- **الأدوات**: بطاقات سيناريو، أوراق حساب.
+#### المحطة 4: لعبة المحاكاة (10 دقائق)
+- **المحتوى**: تطبيق عملي لجمع وطرح النقود في سياق السوق.
+- **النشاط**: إنشاء سوق صغير في الفصل، حيث يقوم الطلاب بدور البائع والمشتري. يتعين على الطلاب استخدام النقود لجمع وطرح المبالغ عند الشراء والبيع.
+- **الأدوات**: قطع نقدية، بطاقات أسعار، أدوات لتمثيل المنتجات.
+### 📝 **أداة قياس الأثر:**
+- مراقبة أداء الطلاب في كل محطة وتقديم تعليقات فورية.
+- استخدام استبيان بسيط في نهاية الدرس لجمع آراء الطلاب حول ما تعلموه وكيف يشعرون بشأن مهاراتهم الجديدة.
+### الملاحظات:
+- يجب على المعلم دعم الطلاب الذين يواجهون صعوبة في فهم المفاهيم من خلال تقديم أمثلة إضافية.
+- ينبغي تعزيز التعاون والتفاعل بين الطلاب، مما يعزز من دعم التعلم الجماعي.
+### الخاتمة:
+خطة الدرس هذه تهدف إلى سد الفجوة التعليمية عن طريق تقديم مفاهيم جمع وطرح النقود بطريقة تفاعلية وممتعة، مما يعزز الفهم لدى الطلاب ويدعم تحقيق الهدف التعليمي.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/School_Data.xlsx
+++ b/School_Data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Teachers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Evaluations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teachers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluations" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2396,20 +2396,16 @@
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>1679428506</t>
-        </is>
+      <c r="B45" t="n">
+        <v>1679428506</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
           <t>جمع وطرح النقود</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D45" t="n">
+        <v>2</v>
       </c>
       <c r="E45" t="n">
         <v>3</v>
@@ -2468,6 +2464,153 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1679428506</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>التمثيل البياني بالاعمدة</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>**خطة درس أولية: التمثيل البياني بالأعمدة**
+**الهدف**: قراءة ورسم الأعمدة البيانية.
+**الفئة المستهدفة**: طلاب الصف (حدد الصف وفقًا لمستوى الفهم).
+**المدة الزمنية**: 40 دقيقة.
+**الاستراتيجية**: التعلم المتمركز حول الطالب من خلال لعبة تعليمية عميقة (Simulation/Role Play).
+### **المكونات الأساسية للنشاط:**
+#### **المقدمة (5 دقائق)**
+- **التمهيد**: استعراض سريع للتمثيل البياني بالأعمدة. 
+- يطرح المعلم سؤالاً عن ما يعرفه الطلاب عن الأعمدة البيانية.
+#### **الأنشطة الرئيسية (30 دقيقة)**
+##### **محطة 1: قراءة الأعمدة البيانية (10 دقائق)**
+- **النشاط**: توزيع ورقة عمل تحتوي على عمود بياني يظهر بيانات مختلفة (مثل: درجات طلاب في مادة معينة).
+- **المهمة**: يقوم الطلاب بقراءة العمود البياني والإجابة على أسئلة تتعلق بالبيانات المعروضة (مثل: من حقق أعلى درجة؟ كم عدد الطلاب الذين حصلوا على درجات تفوق 70؟).
+##### **محطة 2: رسم الأعمدة البيانية (10 دقائق)**
+- **النشاط**: توفير أدوات رسم (ورق، ألوان، مسطرة) لكل طالب.
+- **المهمة**: يقوم الطلاب بجمع بيانات بسيطة (مثل: عدد الطلاب الذين يفضلون فواكه معينة) ثم رسم العمود البياني الخاص بهذه البيانات.
+##### **محطة 3: لعب الأدوار (10 دقائق)**
+- **النشاط**: تقسيم الطلاب إلى مجموعات صغيرة. يتم تعيين دور لكل طالب (مثل: جامع بيانات، رسام، ومحلل).
+- **المهمة**: يقوم الطلاب بجمع البيانات من زملائهم في الفصل حول موضوع معين (مثل: أنواع الهوايات المفضلة) ثم رسم العمود البياني في مجموعاتهم.
+#### **الخاتمة (5 دقائق)**
+- **المشاركة**: يشارك الطلاب النتائج التي حصلوا عليها من محطات النشاط.
+- **التقييم السريع**: يطرح المعلم أسئلة سريعة للتأكد من فهم الطلاب لكيفية قراءة ورسم الأعمدة البيانية.
+### **الموارد المطلوبة**:
+- أوراق عمل تحتوي على أعمدة بيانية.
+- أدوات رسم (ورق، ألوان، مسطرة).
+- بيانات بسيطة لجمعها (يتم إعدادها مسبقًا).
+### **التقييم**:
+- يتم تقييم الطلاب من خلال مشاركتهم في الأنشطة الخاصة بالمحطات الثلاث.
+- يمكن استخدام استبيان بسيط بعد النشاط لقياس مدى فهمهم للموضوع.
+### **ملاحظات**:
+- التأكد من أن كل محطة تتضمن تحديات متوازنة لضمان عدم إرباك الطلاب.
+- تشجيع الطلاب على التعاون والتفاعل أثناء النشاط. 
+بهذه الطريقة، ستعزز الخطة من فهم الطلاب للتمثيل البياني بالأعمدة، مع العمل على سد الفجوة التعليمية وتحفيز المشاركة الفعالة.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1679428506</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>الاشكال والانماط</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>### خطة درس أولية: "الأشكال والأنماط"
+#### الهدف العام:
+تكوين الأنماط واستكمالها من خلال نشاطات تعليمية تفاعلية تعزز من مهارات الطلاب.
+#### الفئة المستهدفة:
+طلاب في المرحلة الابتدائية (الصفوف 1-3)
+#### المدة:
+40 دقيقة
+#### الفجوة التعليمية:
+25.0%
+#### اتجاه مشاركة الطلاب:
+مستقر (بداية)
+### الخطة:
+#### 1. مقدمة (5 دقائق)
+- **التعريف بالدرس**: تقديم الموضوع بطرح سؤال: "ما هي الأشكال التي نراها حولنا؟" 
+- **النقاش**: دعوة الطلاب لمشاركة أشكال مختلفة من البيئة المحيطة بهم.
+#### 2. تقسيم الطلاب إلى مجموعات (5 دقائق)
+- تقسيم الطلاب إلى 4 مجموعات صغيرة (4-5 طلاب في كل مجموعة).
+- توزيع الأدوار داخل كل مجموعة: متحدث، مساعد، وموثق.
+#### 3. المحطات التعليمية (25 دقيقة)
+**كل محطة تستغرق 5 دقائق، ويفترض على الطلاب التحرك بين المحطات.**
+- **المحطة الأولى: تشكيل الأنماط**
+    - **المواد**: بطاقات ملونة بأشكال مختلفة (مثل مثلث، مربع، دائرة).
+    - **النشاط**: على الطلاب استخدام البطاقات لتكوين نمط معين، ثم استكمال هذا النمط ببطاقات جديدة.
+- **المحطة الثانية: مطابقة الأنماط**
+    - **المواد**: مجموعة من الأشكال موجودة على ورق، وقائمة بأشكال أخرى.
+    - **النشاط**: على الطلاب مطابقة الأشكال في الورقة مع الأشكال الموجودة في القائمة.
+- **المحطة الثالثة: رسم الأنماط**
+    - **المواد**: ورق وأقلام ملونة.
+    - **النشاط**: يقوم الطلاب برسم نمط باستخدام الأشكال التي تعلموها في المحطة الأولى.
+- **المحطة الرابعة: لعبة استكمال الأنماط**
+    - **المواد**: مجموعة من البطاقات تحتوي على أنماط ناقصة.
+    - **النشاط**: يتم إعطاء كل مجموعة نمطًا ناقصًا، وعلى الطلاب التفكير في كيفية استكماله. 
+#### 4. مراجعة وتقييم (5 دقائق)
+- **مشاركة المجموعات**: كل مجموعة تقدم ما أنجزته في محطاتها.
+- **التقييم الذاتي**: سؤال الطلاب عن ما تعلموه وما إذا كانوا يشعرون بأنهم أصبحوا أكثر فهمًا للأشكال والأنماط.
+#### 5. ختام الدرس (5 دقائق)
+- **تلخيص النقاط الرئيسية**: مراجعة ما تم تعلمه.
+- **الواجب المنزلي**: طلب من الطلاب البحث في بيئتهم عن أنماط جديدة وتسجيلها.
+### ملاحظات:
+- يجب على المعلم مراقبة تقدم الطلاب في كل محطة وتقديم المساعدة عند الحاجة.
+- تشجيع الطلاب على التعاون والتفاعل خلال الأنشطة لتعزيز التعلم النشط.
+بهذه الخطة، سيتم تحقيق الهدف التعليمي مع مراعاة الفجوة التعليمية المستهدفة وتعزيز مشاركة الطلاب.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-04-07 08:33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/School_Data.xlsx
+++ b/School_Data.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2535,20 +2535,16 @@
       <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1679428506</t>
-        </is>
+      <c r="B47" t="n">
+        <v>1679428506</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
           <t>الاشكال والانماط</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D47" t="n">
+        <v>2</v>
       </c>
       <c r="E47" t="n">
         <v>2</v>
@@ -2611,6 +2607,45 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1679428506</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>النقود</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>مرحبًا بك! إذا كنت بحاجة إلى أي مساعدة أو استفسار حول المحتوى التعليمي أو أي موضوع آخر، فلا تتردد في طرحه. أنا هنا لمساعدتك.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-04-07 09:14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/School_Data.xlsx
+++ b/School_Data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teachers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Teachers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Evaluations" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2611,20 +2611,16 @@
       <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1679428506</t>
-        </is>
+      <c r="B48" t="n">
+        <v>1679428506</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
           <t>النقود</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D48" t="n">
+        <v>1</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -2643,6 +2639,166 @@
       <c r="I48" t="inlineStr">
         <is>
           <t>2026-04-07 09:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1679428506</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>الوقت</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>### خطة درس أولية: قراءة الساعة بالتمام وبنصف ساعة
+#### **الموضوع:** الوقت
+#### **🎯 **الهدف التربوي:**** قراءة الساعة بالتمام وبنصف ساعة
+#### **مدة الدرس:** 40 دقيقة
+#### **استراتيجية التعلم:** التعلم المتمركز حول الطالب (Student-Centered)
+#### **نوع 🎮 **النشاط التفاعلي المقترح:**** لعبة تعليمية عميقة (Simulation/Role Play)
+---
+### **التمهيد (5 دقائق)**
+1. **مقدمة قصيرة:**
+   - تحدث مع الطلاب عن أهمية معرفة الوقت في حياتنا اليومية.
+   - اطرح أسئلة بسيطة مثل: "متى نذهب إلى المدرسة؟" و"متى نتناول الغداء؟" لتشجيع المشاركة.
+2. **عرض الساعة:**
+   - استخدم ساعة حائط كبيرة أو نموذج ساعة يدوية لعرض الأرقام والدقائق.
+---
+### **النشاط الرئيسي (30 دقيقة)**
+#### **المحطة 1: التعرف على الأرقام (10 دقائق)**
+- **🎯 **الهدف التربوي:**** قراءة الأرقام على الساعة.
+- **🎮 **النشاط التفاعلي المقترح:**** 
+  - قسم الطلاب إلى مجموعات صغيرة.
+  - استخدم بطاقات تحتوي على أرقام من 1 إلى 12.
+  - اطلب من كل مجموعة وضع الأرقام على نموذج الساعة بشكل صحيح.
+  - بمجرد الانتهاء، ناقش إجاباتهم وقدم ملاحظات.
+#### **المحطة 2: قراءة الوقت بالتمام (10 دقائق)**
+- **🎯 **الهدف التربوي:**** قراءة الوقت بالتمام.
+- **🎮 **النشاط التفاعلي المقترح:****
+  - استخدم نموذج ساعة حيث يمكن للطلاب تحريك العقارب.
+  - أعطِ كل طالب بطاقة بها وقت محدد (مثل 2:00، 5:00).
+  - يقرأ الطالب الوقت الموجود على بطاقته ويضبط العقارب على الساعة.
+  - قم بتدوين ملاحظات لتعزيز التعلم ومشاركة التعليقات.
+#### **المحطة 3: قراءة الوقت بنصف ساعة (10 دقائق)**
+- **🎯 **الهدف التربوي:**** قراءة الوقت بنصف ساعة.
+- **🎮 **النشاط التفاعلي المقترح:****
+  - استخدم نفس نموذج الساعة.
+  - أعطِ الطلاب بطاقات بوقت بنصف ساعة (مثل 1:30، 3:30).
+  - يضبط الطلاب العقارب على الوقت المحدد، ثم يتبادل الطلاب الأدوار.
+  - في نهاية المحطة، اطلب من الطلاب مشاركة الوقت الذي قاموا بضبطه.
+---
+### **الختام (5 دقائق)**
+1. **مراجعة سريعة:**
+   - اجمع الطلاب وناقش ما تعلموه.
+   - اطلب من الطلاب مشاركة الوقت الذي وجدوه صعب القراءة وكيف يمكن تحسين ذلك.
+2. **تقييم سريع:**
+   - استخدم أسئلة سريعة لقياس مدى فهم الطلاب لقراءة الوقت (مثلاً، "ما هو الوقت الذي يعبر عن 4:30؟").
+---
+### **المواد المطلوبة:**
+- نموذج ساعة كبيرة أو ساعة حائط.
+- بطاقات بأرقام من 1 إلى 12.
+- بطاقات زمنية بالوقت المطلوب (بالتمام وبنصف ساعة).
+### **تقييم الفجوة التعليمية:**
+- بعد الانتهاء من النشاط، يمكن للمعلم تقييم مدى فهم الطلاب من خلال الملاحظات والمشاركة في المحطات المختلفة. إذا كانت الفجوة لا تزال مرتفعة، يمكن تقديم المزيد من التمارين الفردية في الحصص القادمة.
+### **ملاحظات للمعلّم:**
+- تأكد من تشجيع الطلاب على التعبير عن رأيهم ومشاركة تجاربهم الشخصية مع الوقت.
+- كن مرنًا في التعامل مع الأسئلة والتحديات التي قد تواجه الطلاب.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-04-07 09:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1679428506</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>الوقت</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>### خطة درس أولية: "الوقت" - قراءة الساعة بالتمام وبنصف ساعة
+**المستوى الدراسي**: الصف الثاني الابتدائي  
+**مدة الدرس**: 40 دقيقة  
+**الهدف التعليمي**: قراءة الساعة بالتمام وبنصف ساعة  
+**فجوة التعلم**: 25%  
+**اتجاه الأداء**: مستقر (بداية)  
+#### 1. مقدمة الدرس (5 دقائق)
+- **التحية**: رحب بالطلاب وابدأ بمحادثة قصيرة حول الوقت وأهميته في حياتنا اليومية.
+- **عرض الساعة**: استخدم ساعة حائط أو ساعة تعليمية لشرح الأجزاء الأساسية للساعة (الساعات، الدقائق، العقارب).
+#### 2. نشاط اللعبة التعليمية (30 دقيقة)
+##### محطات التعلم:
+**المحطة 1: قراءة الساعة بالتمام (10 دقائق)**
+- **الوصف**: ضع طلابك في مجموعات صغيرة (3-4 طلاب). استخدم بطاقات تحتوي على ساعات مختلفة (مثل: 1:00، 2:00، 3:00).
+- **النشاط**: على كل مجموعة أن تقرأ الساعة المكتوبة على البطاقة، ومن ثم تعبر عن الوقت باستخدام ساعة تعليمية في محطتهم.
+- **التقييم**: ملاحظة قدرة الطلاب على قراءة الوقت بشكل صحيح.
+**المحطة 2: قراءة الساعة بنصف ساعة (10 دقائق)**
+- **الوصف**: استخدم بطاقات تحتوي على أوقات بنصف ساعة (مثل: 1:30، 2:30، 3:30).
+- **النشاط**: نفس النشاط السابق، لكن مع التركيز على قراءة الوقت بنصف ساعة.
+- **التقييم**: ملاحظة دقة القراءة.
+**المحطة 3: لعبة الدور (10 دقائق)**
+- **الوصف**: اجعل الطلاب يمثلون أدوار مختلفة. أحد الطلاب سيكون "الساعة"، والآخرون يسألون "ما هو الوقت؟".
+- **النشاط**: على "الساعة" أن تجيب باستخدام الوقت الذي تمثله. يمكن للطلاب تغيير الأدوار لضمان ممارسة أكبر.
+- **التقييم**: تقدير الأداء الوظيفي لكل طالب في قراءة الوقت.
+#### 3. الختام (5 دقائق)
+- **مراجعة سريعة**: اجمع الطلاب واطلب منهم مشاركة ما تعلموه في الدرس.
+- **تقييم سريع**: اطلب من الطلاب قراءة ساعة عشوائية أمام زملائهم للتأكد من فهمهم.
+- **توجيهات للمنزل**: شجع الطلاب على ممارسة قراءة الوقت مع أسرهم في البيت.
+### الموارد المطلوبة:
+- ساعة حائط أو ساعة تعليمية
+- بطاقات زمنية (تحتوي على أوقات مختلفة)
+- مساحة كافية لتوزيع المحطات
+### ملاحظات:
+- تأكد من تقديم الدعم للطلاب الذين يواجهون صعوبات.
+- يمكن استخدام تقنيات تحفيزية مثل الجوائز الصغيرة لتشجيع المشاركة.
+بهذه الخطة التعليمية، نضمن استخدام أسلوب التعلم النشط المتمركز حول الطالب، مع توفير بيئة تعليمية تفاعلية تعزز من فهم الطلاب لمفهوم الوقت.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-04-07 09:38</t>
         </is>
       </c>
     </row>

--- a/School_Data.xlsx
+++ b/School_Data.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2733,20 +2733,16 @@
       <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>1679428506</t>
-        </is>
+      <c r="B50" t="n">
+        <v>1679428506</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>الوقت</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D50" t="n">
+        <v>1</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -2802,6 +2798,164 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1679428506</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>الوقت</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>### خطة درس أولية: "الوقت"
+#### 🎯 **الهدف التربوي:**
+تمكين الطلاب من قراءة الوقت بالتمام وبنصف ساعة.
+#### مدة الدرس:
+40 دقيقة
+#### الفئة المستهدفة:
+طلاب الصف الابتدائي (المرحلة الابتدائية).
+#### مقدمة الدرس (5 دقائق):
+- بدء الدرس بمقدمة تفاعلية حول أهمية الوقت في حياتنا اليومية.
+- طرح سؤال للطلاب: "ما هي الأشياء التي نستخدم فيها الوقت؟"
+#### النشاط الرئيسي (30 دقيقة):
+**لعبة تعليمية: "محطات الوقت"**
+**محطة 1: قراءة الساعة (10 دقائق)**
+- *المواد المطلوبة:* ساعات حائط كبيرة وورق وأقلام.
+- *🎮 **النشاط التفاعلي المقترح:*** 
+  - يقوم المعلم بتوزيع ساعات حائط كبيرة على الطلاب.
+  - يطلب من الطلاب تحديد الوقت في كل ساعة مكتوبة على الورق (مثل: 3:00، 6:30).
+  - يتم تقديم المكافآت لأفضل الطلاب الذين يقرأون الوقت بدقة.
+**محطة 2: لعبة الأدوار (10 دقائق)**
+- *المواد المطلوبة:* بطاقات تحتوي على أوقات مختلفة.
+- *🎮 **النشاط التفاعلي المقترح:***
+  - يقوم الطلاب بدور المذيع ويدعو زملائهم لإخبارهم بالوقت المطلوب.
+  - يشجع المعلم الطلاب على استخدام عبارات مثل "الساعة الآن..." ويقوم بتصحيح الأخطاء إذا كانت هناك أي أخطاء في القراءة.
+**محطة 3: تحدي الزمن (10 دقائق)**
+- *المواد المطلوبة:* ساعة زمنية ورق ملون.
+- *🎮 **النشاط التفاعلي المقترح:***
+  - تقسيم الطلاب إلى مجموعتين.
+  - يطلب من كل مجموعة القيام بتحدي قراءة الوقت على الساعة.
+  - يتم منح نقاط لكل مجموعة بناءً على دقة قراءتهم للوقت.
+#### ختام الدرس (5 دقائق):
+- مراجعة مع الطلاب حول ما تعلموه اليوم.
+- طرح بعض الأسئلة التفاعلية لمعرفة مدى فهمهم.
+- تشجيع الطلاب على ممارسة قراءة الوقت في المنزل.
+#### قواعد اللعبة:
+- يجب على الطلاب العمل بشكل جماعي والتعاون.
+- يمكن استخدام أدوات مثل المؤقت لمراقبة الوقت في كل محطة.
+### ملاحظات:
+- التركيز على تعزيز المهارات من خلال اللعب والتفاعل.
+- مراعاة الفجوة التعليمية (25%) من خلال توضيح المفاهيم بشكل مبسط وتقديم الدعم المستمر خلال النشاط.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-04-07 09:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1679428506</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>الاشكال والانماط</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>### خطة درس أولية: الأشكال والأنماط
+**الموضوع:** الأشكال والأنماط  
+**🎯 **الهدف التربوي:**** تكوين الأنماط واستكمالها  
+**المدة:** 40 دقيقة  
+**الفئة المستهدفة:** طلاب المرحلة الابتدائية (الصفوف 1-3)  
+**فجوة التعلم:** 25%  
+**اتجاه الأداء:** مستقر (بداية)  
+**استراتيجية التعلم:** التعلم المتمركز حول الطالب (Student-Centered)  
+**نوع 🎮 **النشاط التفاعلي المقترح:**** لعبة تعليمية عميقة (Simulation/Role Play)  
+#### الأهداف الخاصة بالدرس:
+1. تحسين قدرة الطلاب على التعرف على الأشكال الأساسية (مثل الدائرة، المربع، مثلث، إلخ).
+2. تمكين الطلاب من تكوين الأنماط باستخدام الأشكال المختلفة.
+3. تعزيز التفكير النقدي والقدرة على الاستنتاج من خلال استكمال الأنماط المفقودة.
+#### خطة 🎮 **النشاط التفاعلي المقترح:**
+**المقدمة (5 دقائق):**
+- بدء الدرس بمناقشة سريعة حول الأشكال المختلفة، وطلب من الطلاب إحضار أي شكل يتعرفون عليه من البيئة المحيطة بهم.
+- تقديم مفهوم الأنماط وكيفية تكوينها باستخدام الأشكال.
+**النشاط الرئيسي (30 دقيقة):**
+*محطات تعليمية متعددة:*
+1. **محطة التعرف على الأشكال (10 دقائق):**
+   - وضع عدة أشكال (مربعات، مثلثات، دوائر) على الطاولة.
+   - يقوم الطلاب بجولة في المحطة والتعرف على كل شكل، مع تلقي معلومات موجزة عن كل شكل.
+   - يتم إعطاء الطلاب بطاقات تحتوي على أسماء الأشكال، وعليهم مطابقتها مع الأشكال الموجودة.
+2. **محطة الأنماط البصرية (10 دقائق):**
+   - توزيع مجموعة من البطاقات تحتوي على أنماط مختلفة (مثل: دائرة، مثلث، دائرة، مثلث..).
+   - يطلب من الطلاب تكوين نمط جديد باستخدام الأشكال المتاحة، وبناء نمط جديد خاص بهم.
+   - يمكن للطلاب العمل بمجموعات صغيرة لتبادل الأفكار.
+3. **محطة الاستكمال (10 دقائق):**
+   - إعداد رسوم بيانية أو بطاقات تحتوي على أنماط غير مكتملة (مثل: مربع، دائرة، مربع، ؟).
+   - يقوم الطلاب بمهمة إكمال الأنماط المفقودة باستخدام الأشكال المناسبة.
+   - دعوة الطلاب لمشاركة الأنماط التي أنشأوها مع بقية الصف.
+**الختام (5 دقائق):**
+- مناقشة ما تعلمه الطلاب في كل محطة.
+- تشجيع الطلاب على التفكير في كيفية استخدام الأنماط في حياتهم اليومية، ومشاركة أي أمثلة.
+#### أدوات ومواد:
+- بطاقات أشكال (دوائر، مثلثات، مربعات).
+- بطاقات الأنماط.
+- أدوات تلوين ورقية.
+- ورق مقوى لتثبيت الأشكال.
+#### ملاحظات للمعلم:
+- تأكد من توزيع الطلاب على المحطات بالتساوي.
+- قم بتشجيع الطلاب على التعاون والمشاركة في الأنشطة.
+- استخدم أسئلة مفتوحة لتحفيز التفكير النقدي.
+### تقييم:
+- ملاحظة أداء الطلاب في كل محطة.
+- إجراء تقييم غير رسمي من خلال الملاحظات والتفاعل مع الطلاب.
+بهذه الخطة، نأمل أن نساعد الطلاب على سد الفجوة التعليمية من خلال الأنشطة التفاعلية التي تعزز التعلم وتوفر تجربة تعليمية ممتعة.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-04-07 20:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/School_Data.xlsx
+++ b/School_Data.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2875,20 +2875,16 @@
       <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>1679428506</t>
-        </is>
+      <c r="B52" t="n">
+        <v>1679428506</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
           <t>الاشكال والانماط</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D52" t="n">
+        <v>2</v>
       </c>
       <c r="E52" t="n">
         <v>2</v>
@@ -2956,6 +2952,89 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1679428506</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>الوقت</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>**خطة درس: قراءة الساعة بالتمام وبنصف ساعة**
+**الموضوع:** الوقت  
+**الهدف من الدرس:** قراءة الساعة بالتمام وبنصف ساعة  
+**مدة الدرس:** 40 دقيقة  
+**فجوة التعلم:** 25%  
+**استراتيجية التعلم:** متمركزة حول الطالب (Student-Centered)  
+**أسلوب 🎮 **النشاط التفاعلي المقترح:**** لعبة تعليمية عميقة (Simulation/Role Play)  
+**مستوى الصعوبة:** متوسط  
+### 1. التحضير للدرس:
+- **الأدوات المطلوبة:**
+  - ساعات حائط وهمية (يمكن استخدامها كوسيلة تعليمية).
+  - بطاقات مكتوب عليها أوقات مختلفة (مثل: 3:00، 4:30، 6:00).
+  - أوراق عمل تتضمن تمارين القراءة للساعة.
+  - أدوات للكتابة (أقلام، أوراق).
+### 2. مقدمة (5 دقائق):
+- **الترحيب بالطلاب:** بدء الدرس بتحية ودية.
+- **مقدمة حول الموضوع:** شرح أهمية معرفة قراءة الساعة في الحياة اليومية.
+- **تحديد الأهداف:** إخبار الطلاب بما سيتعلمونه في الدرس.
+### 3. الأنشطة التعليمية (30 دقيقة):
+**النشاط الأول: محطات التعلم (15 دقيقة)**
+- **تقسيم الطلاب إلى مجموعات صغيرة (4-5 طلاب).**
+- **تحديد 3 محطات تعليمية، كل محطة تتضمن نشاطًا مختلفًا:**
+  1. **محطة القراءة بالتمام:**
+     - الطلاب سيقومون بقراءة الساعة الموجودة في محطة (ساعة حائط وهمية) والإشارة إلى الوقت المناسب.
+  2. **محطة القراءة بنصف ساعة:**
+     - الطلاب سيقومون بقراءة الأوقات المكتوبة على البطاقات وتحديد ما إذا كانت الساعة بالتمام أو بنصف ساعة.
+  3. **محطة التمارين التفاعلية:**
+     - استخدام أوراق العمل التي تحتوي على تمارين قراءة الساعة، حيث يقوم الطلاب بالإجابة عن الأسئلة بشكل فردي.
+**النشاط الثاني: لعبة الأدوار (15 دقيقة)**
+- **توزيع الأدوار على الطلاب:**
+  - بعض الطلاب سيلعبون دور "الساعة" (بإظهار الوقت من خلال التمثيل).
+  - الآخرون سيقومون بدور "المعلم" (طرح الأسئلة وقراءة الوقت).
+- **إجراء اللعبة:**
+  - يقوم الطلاب بتبادل الأدوار، حيث يتمكن كل طالب من ممارسة قراءة الساعة بالتفاعل مع زملائه.
+### 4. الخاتمة (5 دقائق):
+- **مراجعة سريعة:** تلخيص ما تم تعلمه خلال الدرس.
+- **طرح أسئلة للطلاب:** التأكد من فهمهم للموضوع.
+- **توزيع واجب منزلي:** كتابة 5 أوقات مختلفة وقراءتها.
+### 5. 📝 **أداة قياس الأثر:**
+- **ملاحظة أداء الطلاب:** تقييم دقة قراءة الساعة من خلال الملاحظات أثناء الأنشطة.
+- **تقييم المشاركة:** مراقبة التفاعل والاستجابة أثناء اللعبة.
+### 6. التعزيز:
+- **تقديم ملاحظات إيجابية:** تعزيز الطلاب الذين أظهروا تقدمًا في قراءة الساعة.
+- **توفير دعم إضافي للطلاب الذين يحتاجون مساعدة إضافية.**
+بهذه الطريقة، ستتيح هذه الخطة للطلاب تعلم قراءة الساعة بطريقة ممتعة وتفاعلية، مما يساعد في سد الفجوة التعليمية وتحقيق الهدف المطلوب.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-04-07 23:09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/School_Data.xlsx
+++ b/School_Data.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,20 +2956,16 @@
       <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1679428506</t>
-        </is>
+      <c r="B53" t="n">
+        <v>1679428506</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
           <t>الوقت</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D53" t="n">
+        <v>1</v>
       </c>
       <c r="E53" t="n">
         <v>2</v>
@@ -3035,6 +3031,100 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1679428506</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>الطرح البسيط</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>### خطة درس أولية: 'الطرح البسيط'
+#### الموضوع: فهم مفهوم الطرح كأخذ جزء من الكل
+#### الفئة المستهدفة: الطلاب في الصف الأول الابتدائي
+#### المدة: 40 دقيقة
+#### الفجوة التعليمية: 25.0%
+#### اتجاه الأداء: مستقر (بداية)
+---
+#### **الأهداف التعليمية:**
+1. فهم مفهوم الطرح كأخذ جزء من الكل.
+2. تعزيز مهارات الطرح من خلال الأنشطة التفاعلية.
+3. تطوير التفكير النقدي لدى الطلاب من خلال الممارسة العملية.
+---
+### **نشاط اللعبة التعليمية: "محطات الطرح"**
+#### **المرحلة 1: مقدمة (5 دقائق)**
+- يبدأ المعلم بشرح بسيط لمفهوم الطرح من خلال استخدام أمثلة مرئية (مثل تفاحة معروضة، وطرح عدد منها).
+- يوضح الفكرة بأن الطرح يعني أخذ جزء من الكل.
+#### **المرحلة 2: تقسيم الطلاب إلى مجموعات (5 دقائق)**
+- يقسم المعلم الطلاب إلى مجموعات صغيرة (4 طلاب في كل مجموعة).
+- يقدم لكل مجموعة بطاقة تحتوي على مسألة طرح بسيطة (مثل 5 - 2).
+#### **المرحلة 3: محطات التعلم (25 دقيقة)**
+- يتم إعداد 4 محطات تعليمية مختلفة، حيث يقضي الطلاب 5 دقائق في كل محطة:
+##### **المحطة 1: محطة الفواكه**
+- استخدام كرات ملونة أو فواكه مصنوعة من الورق.
+- يقوم الطلاب بأخذ عدد معين من الكرات، ثم يطرحون منها عددًا محددًا.
+- يشرح كل طالب لزملائه ما حدث.
+##### **المحطة 2: محطة الأرقام**
+- استخدام بطاقات الأرقام.
+- يقوم الطلاب بسحب بطاقتين (مثل 7 و3)، ثم يقومون بطرح الرقمين باستخدام البطاقات.
+- يشجع المعلم الطلاب على مناقشة النتائج مع بعضهم.
+##### **المحطة 3: محطة القصص**
+- يقدم المعلم قصة قصيرة تتضمن عملية طرح.
+- يطلب من الطلاب تمثيل القصة من خلال اللعب، حيث يقوم أحدهم بأخذ جزء من الكل (مثل: "كان هناك 6 طيور في الشجرة، طار 2 منهم، كم تبقى؟").
+##### **المحطة 4: محطة اللوحات**
+- يقدم المعلم لوحات بيضاء وأقلام.
+- يقوم الطلاب بإنشاء معادلات طرح خاصة بهم ورسم صور توضح الفكرة.
+- يسمح للطلاب بمشاركة لوحاتهم مع باقي المجموعات.
+#### **المرحلة 4: تقييم التعلم (5 دقائق)**
+- يقوم المعلم بجمع المجموعات معًا ويسألهم أسئلة تفاعلية حول ما تعلموه.
+- يمكن استخدام أسئلة مثل:
+  - ما هو الطرح؟
+  - كيف يمكننا استخدام الطرح في حياتنا اليومية؟
+---
+### **المواد المطلوبة:**
+- كرات ملونة أو فواكه ورقية.
+- بطاقات أرقام.
+- بطاقات مع مسائل طرح.
+- لوحات بيضاء وأقلام.
+### **ملاحظات:**
+- التأكد من توفير بيئة تعليمية إيجابية وداعمة.
+- يجب أن تكون الأنشطة ممتعة وتشجع على التعاون بين الطلاب.
+- يمكن للمعلم تعديل المحطات حسب احتياجات الطلاب ومستوى فهمهم.
+### **التقييم والمتابعة:**
+- استخدام ملاحظات المعلم خلال النشاط لتحديد مدى فهم الطلاب للمفهوم.
+- يمكن إجراء اختبار قصير في الدروس التالية لتقييم التقدم المحرز في فهم الطرح.
+---
+هذه الخطة مصممة لتعزيز فهم الطلاب لمفهوم الطرح من خلال الأنشطة العملية والتفاعلية، مما يساعد في تقليل الفجوة التعليمية وتعزيز المشاركة.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-04-12 15:29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/School_Data.xlsx
+++ b/School_Data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Teachers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Evaluations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teachers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluations" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3035,20 +3035,16 @@
       <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>1679428506</t>
-        </is>
+      <c r="B54" t="n">
+        <v>1679428506</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
           <t>الطرح البسيط</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D54" t="n">
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>3</v>
@@ -3125,6 +3121,177 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1679428506</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>الوقت</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>### خطة درس أولية: قراءة الساعة بالتمام وبنصف ساعة
+#### الموضوع: الوقت
+#### المدة: 40 دقيقة
+#### الفئة المستهدفة: طلاب المرحلة الابتدائية (الصف الثاني)
+#### 🎯 **الهدف التربوي:** تمكين الطلاب من قراءة الساعة بالتمام وبنصف ساعة
+---
+### الأهداف التعليمية:
+1. أن يتمكن الطلاب من قراءة الساعة بدقة.
+2. أن يستطيع الطلاب تحديد الوقت بالتمام (مثل 2:00) وبنصف ساعة (مثل 2:30).
+---
+### أدوات ومواد:
+- ساعات تعليمية (ساعات ورقية أو ساعات حقيقية).
+- بطاقات زمنية مكتوب عليها أوقات مختلفة.
+- محطات تعليمية (مراكز) لكل نشاط.
+- أوراق عمل لتمارين إضافية.
+---
+### تصميم 🎮 **النشاط التفاعلي المقترح:**
+يتم تنظيم الدرس في شكل لعبة تعليمية تتضمن محطات تعليمية متعددة، حيث يتنقل الطلاب بين المحطات ويشاركون في أنشطة تفاعلية تعزز من فهمهم للوقت.
+#### المحطة 1: "ساعة الأصدقاء"
+- **النشاط**: يقوم الطلاب بتشكيل أزواج، حيث يقوم أحدهم بإظهار الوقت على الساعة (الورقية) والآخر يقرأ الوقت.
+- **الهدف**: تعزيز مهارات القراءة بالتماثل.
+#### المحطة 2: "البطاقة الزمنية"
+- **النشاط**: توزيع بطاقات زمنية تحمل أوقات مختلفة. يجب على الطلاب مطابقة الوقت المكتوب على البطاقة مع الوقت المقابل على الساعة.
+- **الهدف**: تعزيز الربط بين الوقت المكتوب والمقروء.
+#### المحطة 3: "صانع الوقت"
+- **النشاط**: يقوم الطلاب بإنشاء ساعة ورقية خاصة بهم، حيث يقومون بتدوين أوقات مختلفة بالتمام وبنصف ساعة. يتم تبادل الساعات مع زملائهم لقراءة الوقت المكتوب.
+- **الهدف**: تعزيز الفهم الإبداعي للوقت.
+#### المحطة 4: "سباق الوقت"
+- **النشاط**: تنظيم مسابقة حيث يتسابق الطلاب في قراءة أوقات مختلفة من الساعات المعروضة. يتم احتساب النقاط لكل قراءة صحيحة.
+- **الهدف**: تعزيز سرعة الفهم والقراءة.
+---
+### 📝 **أداة قياس الأثر:**
+- استخدام المراقبة والملاحظة أثناء الأنشطة لتقييم فهم الطلاب.
+- تقديم أوراق عمل بعد الانتهاء من المحطات لتطبيق المهارات المكتسبة، حيث يتم تقييم الطلاب بناءً على الدقة في قراءة الوقت.
+---
+### الخاتمة:
+- مناقشة سريعة مع الطلاب حول ما تعلموه.
+- تشجيع الطلاب على استخدام المهارات المكتسبة في الحياة اليومية.
+---
+### التعليمات الإضافية:
+- يجب التأكد من مشاركة جميع الطلاب في كل محطة.
+- يمكن تعديل مستوى صعوبة الأنشطة بناءً على استجابة الطلاب.
+---
+هذه الخطة تهدف إلى سد الفجوة التعليمية بشكل فعال وتوفير بيئة تعليمية تفاعلية تعزز من فهم الطلاب للوقت.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-04-14 02:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1679428506</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>الوقت</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>**خطة درس أولية: "الوقت - قراءة الساعة بالتمام وبنصف ساعة"**
+**المدة:** 40 دقيقة  
+**الفئة العمرية:** 7-9 سنوات  
+**المستوى التعليمي:** مبتدئ  
+**الفجوة التعليمية:** 25.0%  
+**اتجاه المشاركة:** مستقر (بداية)  
+**الاستراتيجية:** التعلم المتمركز حول الطالب (Student-Centered)  
+**نوع 🎮 **النشاط التفاعلي المقترح:**** لعبة تعليمية (Simulation/Role Play)
+---
+### **أهداف الدرس:**
+1. قراءة الساعة بالتمام وبنصف ساعة.
+2. تعزيز مهارات التفاعل والتعاون بين الطلاب.
+3. تعزيز الفهم العملي لمفهوم الوقت.
+---
+### **المواد المطلوبة:**
+- ساعات ملونة (صنع يدوي أو مطبوعة).
+- بطاقات تحتوي على أوقات مختلفة (مثل 1:00، 1:30، 2:00، 2:30...).
+- لوحات بيضاء صغيرة وأقلام.
+- مساحات تعليمية (محطات) معدة مسبقًا.
+---
+### **الخطوات:**
+#### **المقدمة (5 دقائق):**
+1. **الترحيب بالطلاب** وتعريفهم بموضوع الدرس.
+2. **عرض مختصر** لأهمية تعلم قراءة الوقت وكيف يساعدنا في الحياة اليومية.
+#### **النشاط الرئيسي (30 دقيقة):**
+**محطات تعليمية متعددة (كل محطة 7 دقائق):**
+1. **المحطة الأولى: "ساعة المرح"**
+   - يقوم الطلاب بتكوين مجموعات صغيرة.
+   - يتم إعطاؤهم ساعات ملونة، وعليهم ضبط العقارب على الوقت المدون على البطاقات.
+   - كل مجموعة تتسابق لمعرفة من يمكنه ضبط الساعة بشكل صحيح في أقل وقت ممكن.
+2. **المحطة الثانية: "البحث عن الوقت"**
+   - يتم توزيع بطاقات تحتوي على أوقات مختلفة.
+   - على الطلاب استخدام لوحاتهم الصغيرة لتدوين الوقت الذي يظهر على البطاقات.
+   - بعد الانتهاء، يقوم الطلاب بمشاركة إجاباتهم مع مجموعاتهم.
+3. **المحطة الثالثة: "محاكاة الحياة اليومية"**
+   - يقوم الطلاب بدور شخصيات (مثل موظف، طالب، أو أم) ويحتاج كل منهم إلى تحديد الوقت المناسب لأداء مهامه.
+   - على كل طالب استخدام الساعة الملونة للإشارة إلى الوقت الذي يحتاجونه.
+   - يتم تشجيع الطلاب على استخدام عبارات مثل "الساعة الآن..." أو "علي أن أكون في المدرسة الساعة...".
+4. **المحطة الرابعة: "لعبة الأوقات"**
+   - لعبة جماعية حيث يطلب المعلم من طالب تحديد الوقت بشكل عشوائي، وعليه أن يتشارك مع الجميع.
+   - الطلاب يقومون بتحديد الوقت على ساعاتهم والتأكيد على الإجابة الصحيحة.
+#### **الخاتمة (5 دقائق):**
+1. **جلسة مراجعة سريعة**: إعادة طرح الأسئلة على الطلاب حول ما تعلموه.
+2. **تشجيع الطلاب** على مشاركة ما استمتعوا به خلال النشاط.
+3. **تقديم واجب منزلي بسيط**: طلب منهم أن يبحثوا عن أوقات مختلفة في حياتهم اليومية ويقوموا بتدوينها.
+---
+### **📝 **أداة قياس الأثر:****
+- ملاحظة تفاعل الطلاب في المحطات التعليمية.
+- تقييم دقة إجابات الطلاب أثناء الأنشطة.
+- مشاركة الطلاب في نهاية الدرس للتأكد من فهمهم للمفاهيم.
+--- 
+### **ملاحظات:**
+- ضرورة وجود مرشدين أو معلمين مساعدين في كل محطة لدعم الطلاب.
+- التأكد من أن كل محطة تقدم تحديات متوازنة تناسب مستوى الطلاب.
+بهذه الطريقة، يمكن تحقيق الهدف التعليمي من خلال مشاركة الطلاب بشكل نشط وتعزيز الفهم العملي لمفهوم الوقت.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>غير معروف</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-04-14 02:49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
